--- a/city_demand_matrix.xlsx
+++ b/city_demand_matrix.xlsx
@@ -18,94 +18,94 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="30">
   <si>
-    <t>Barcelona</t>
+    <t>BAR</t>
   </si>
   <si>
-    <t>Belgium(Bruxelles-Antwerp-Lille)</t>
+    <t>BEL</t>
   </si>
   <si>
-    <t>Berlin</t>
+    <t>BER</t>
   </si>
   <si>
-    <t>Bilbao</t>
+    <t>BIL</t>
   </si>
   <si>
-    <t>Bordeaux</t>
+    <t>BOR</t>
   </si>
   <si>
-    <t>Bremen</t>
+    <t>BRE</t>
   </si>
   <si>
-    <t>Düsseldorf</t>
+    <t>DUS</t>
   </si>
   <si>
-    <t>Frankfurt am Main-Mannheim-Ludwigshafen</t>
+    <t>FRA</t>
   </si>
   <si>
-    <t>Hamburg</t>
+    <t>HAN</t>
   </si>
   <si>
-    <t>Hannover</t>
+    <t>HAM</t>
   </si>
   <si>
-    <t>Köln</t>
+    <t>KOL</t>
   </si>
   <si>
-    <t>Lisboa</t>
+    <t>LIS</t>
   </si>
   <si>
-    <t>Lyon</t>
+    <t>LYO</t>
   </si>
   <si>
-    <t>Madrid</t>
+    <t>MAD</t>
   </si>
   <si>
-    <t>Marseille</t>
+    <t>MAR</t>
   </si>
   <si>
-    <t>Milano</t>
+    <t>MIL</t>
   </si>
   <si>
-    <t>München</t>
+    <t>MUN</t>
   </si>
   <si>
-    <t>Nantes</t>
+    <t>NAN</t>
   </si>
   <si>
-    <t>Napoli</t>
+    <t>NAP</t>
   </si>
   <si>
-    <t>Netherlands(Amsterdam, Hague, Rotterdam)</t>
+    <t>NED</t>
   </si>
   <si>
-    <t>Nürnberg</t>
+    <t>NUR</t>
   </si>
   <si>
-    <t>Paris</t>
+    <t>PAR</t>
   </si>
   <si>
-    <t>Porto</t>
+    <t>POR</t>
   </si>
   <si>
-    <t>Roma</t>
+    <t>ROM</t>
   </si>
   <si>
-    <t>Ruhrgebiet</t>
+    <t>RUH</t>
   </si>
   <si>
-    <t>Sevilla</t>
+    <t>SEV</t>
   </si>
   <si>
-    <t>Stuttgart</t>
+    <t>STU</t>
   </si>
   <si>
-    <t>Torino</t>
+    <t>TOR</t>
   </si>
   <si>
-    <t>Toulouse</t>
+    <t>TOU</t>
   </si>
   <si>
-    <t>Valencia</t>
+    <t>VAL</t>
   </si>
 </sst>
 </file>
@@ -121,9 +121,9 @@
     </font>
     <font>
       <b/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
